--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -36,7 +36,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -46,6 +46,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -453,7 +453,7 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.550625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26.970625000000002" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -111,47 +111,47 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/SheetProtection.xlsx
@@ -453,7 +453,7 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.970625000000002" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26.970625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
